--- a/excel-projects/class_survey_results_v2.xlsx
+++ b/excel-projects/class_survey_results_v2.xlsx
@@ -1,21 +1,35 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
-  <fileVersion appName="xl" lastEdited="6" lowestEdited="6" rupBuild="14420"/>
-  <workbookPr defaultThemeVersion="153222"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\USER\Documents\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\data-analytics-repo\excel-projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1539C587-180A-4943-B5DD-F719713DB0AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="19200" windowHeight="7190" activeTab="1"/>
+    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="class_survey_results_v2" sheetId="1" r:id="rId1"/>
     <sheet name="Sheet1" sheetId="2" r:id="rId2"/>
   </sheets>
-  <calcPr calcId="152511"/>
+  <calcPr calcId="191029"/>
+  <extLst>
+    <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
+      <xcalcf:calcFeatures>
+        <xcalcf:feature name="microsoft.com:RD"/>
+        <xcalcf:feature name="microsoft.com:Single"/>
+        <xcalcf:feature name="microsoft.com:FV"/>
+        <xcalcf:feature name="microsoft.com:CNMTM"/>
+        <xcalcf:feature name="microsoft.com:LET_WF"/>
+        <xcalcf:feature name="microsoft.com:LAMBDA_WF"/>
+        <xcalcf:feature name="microsoft.com:ARRAYTEXT_WF"/>
+      </xcalcf:calcFeatures>
+    </ext>
+  </extLst>
 </workbook>
 </file>
 
@@ -115,8 +129,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
-  <fonts count="18" x14ac:knownFonts="1">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="19" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -247,6 +261,13 @@
     <font>
       <sz val="11"/>
       <color theme="0"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="14"/>
+      <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
       <scheme val="minor"/>
@@ -593,8 +614,9 @@
     <xf numFmtId="0" fontId="1" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="17" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="1">
+  <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
+    <xf numFmtId="0" fontId="18" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
   <cellStyles count="42">
     <cellStyle name="20% - Accent1" xfId="19" builtinId="30" customBuiltin="1"/>
@@ -914,460 +936,527 @@
 </a:theme>
 </file>
 
+<file path=xl/webextensions/taskpanes.xml><?xml version="1.0" encoding="utf-8"?>
+<wetp:taskpanes xmlns:wetp="http://schemas.microsoft.com/office/webextensions/taskpanes/2010/11">
+  <wetp:taskpane dockstate="right" visibility="0" width="525" row="0">
+    <wetp:webextensionref xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+  </wetp:taskpane>
+</wetp:taskpanes>
+</file>
+
+<file path=xl/webextensions/webextension1.xml><?xml version="1.0" encoding="utf-8"?>
+<we:webextension xmlns:we="http://schemas.microsoft.com/office/webextensions/webextension/2010/11" id="{6E420754-0849-4AE0-B80C-2A4AAA5E1CBB}">
+  <we:reference id="wa200010215" version="2.0.0.0" store="en-US" storeType="OMEX"/>
+  <we:alternateReferences>
+    <we:reference id="wa200010215" version="2.0.0.0" store="wa200010215" storeType="OMEX"/>
+  </we:alternateReferences>
+  <we:properties/>
+  <we:bindings/>
+  <we:snapshot xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships"/>
+</we:webextension>
+</file>
+
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:M16"/>
-  <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
+  <sheetFormatPr defaultRowHeight="18.5" x14ac:dyDescent="0.45"/>
   <cols>
-    <col min="1" max="1" width="15.90625" customWidth="1"/>
-    <col min="2" max="2" width="23.36328125" customWidth="1"/>
-    <col min="3" max="3" width="25.1796875" customWidth="1"/>
-    <col min="4" max="4" width="26.90625" customWidth="1"/>
-    <col min="5" max="5" width="24.90625" customWidth="1"/>
-    <col min="8" max="8" width="12.90625" customWidth="1"/>
-    <col min="9" max="9" width="11" customWidth="1"/>
-    <col min="10" max="10" width="16.1796875" customWidth="1"/>
-    <col min="11" max="11" width="9.6328125" customWidth="1"/>
-    <col min="12" max="12" width="14" customWidth="1"/>
+    <col min="1" max="1" width="15.90625" style="1" customWidth="1"/>
+    <col min="2" max="2" width="23.36328125" style="1" customWidth="1"/>
+    <col min="3" max="3" width="25.1796875" style="1" customWidth="1"/>
+    <col min="4" max="4" width="26.90625" style="1" customWidth="1"/>
+    <col min="5" max="5" width="24.90625" style="1" customWidth="1"/>
+    <col min="6" max="7" width="8.7265625" style="1"/>
+    <col min="8" max="8" width="12.90625" style="1" customWidth="1"/>
+    <col min="9" max="9" width="11" style="1" customWidth="1"/>
+    <col min="10" max="10" width="16.1796875" style="1" customWidth="1"/>
+    <col min="11" max="11" width="9.6328125" style="1" customWidth="1"/>
+    <col min="12" max="12" width="14" style="1" customWidth="1"/>
+    <col min="13" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A1" t="s">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
-      <c r="B1" t="s">
+      <c r="B1" s="1" t="s">
         <v>1</v>
       </c>
-      <c r="C1" t="s">
+      <c r="C1" s="1" t="s">
         <v>2</v>
       </c>
-      <c r="D1" t="s">
+      <c r="D1" s="1" t="s">
         <v>3</v>
       </c>
-      <c r="E1" t="s">
+      <c r="E1" s="1" t="s">
         <v>4</v>
       </c>
-      <c r="F1" t="s">
+      <c r="F1" s="1" t="s">
         <v>5</v>
       </c>
-      <c r="H1" t="s">
+      <c r="H1" s="1" t="s">
         <v>18</v>
       </c>
-      <c r="I1" t="s">
+      <c r="I1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="J1" t="s">
+      <c r="J1" s="1" t="s">
         <v>20</v>
       </c>
-      <c r="K1" t="s">
+      <c r="K1" s="1" t="s">
         <v>19</v>
       </c>
-      <c r="L1" t="s">
+      <c r="L1" s="1" t="s">
         <v>21</v>
       </c>
-      <c r="M1" t="s">
+      <c r="M1" s="1" t="s">
         <v>19</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A2">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A2" s="1">
         <v>101</v>
       </c>
-      <c r="B2" t="s">
+      <c r="B2" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C2">
+      <c r="C2" s="1">
         <v>10</v>
       </c>
-      <c r="D2" t="s">
+      <c r="D2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E2" t="s">
+      <c r="E2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F2">
+      <c r="F2" s="1">
         <v>85</v>
       </c>
-      <c r="H2" t="str">
+      <c r="H2" s="1" t="str">
         <f>B2</f>
         <v>Math</v>
       </c>
-      <c r="I2">
+      <c r="I2" s="1">
         <f>COUNTIF(B2:B16,H2)</f>
         <v>4</v>
       </c>
-      <c r="J2" t="s">
+      <c r="J2" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="K2">
+      <c r="K2" s="1">
         <f>COUNTIF($D$2:$D$16,J2)</f>
         <v>5</v>
       </c>
-      <c r="L2" t="s">
+      <c r="L2" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="M2">
+      <c r="M2" s="1">
         <f>COUNTIF($E$2:$E$16,L2)</f>
         <v>6</v>
       </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A3">
+    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A3" s="1">
         <v>102</v>
       </c>
-      <c r="B3" t="s">
+      <c r="B3" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C3">
+      <c r="C3" s="1">
         <v>8</v>
       </c>
-      <c r="D3" t="s">
+      <c r="D3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E3" t="s">
+      <c r="E3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F3">
+      <c r="F3" s="1">
         <v>78</v>
       </c>
-      <c r="H3" t="str">
+      <c r="H3" s="1" t="str">
         <f t="shared" ref="H3:H5" si="0">B3</f>
         <v>Science</v>
       </c>
-      <c r="I3">
+      <c r="I3" s="1">
         <f t="shared" ref="I3:I5" si="1">COUNTIF(B3:B17,H3)</f>
         <v>5</v>
       </c>
-      <c r="J3" t="s">
+      <c r="J3" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="K3">
+      <c r="K3" s="1">
         <f t="shared" ref="K3:K5" si="2">COUNTIF($D$2:$D$16,J3)</f>
         <v>3</v>
       </c>
-      <c r="L3" t="s">
+      <c r="L3" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="M3">
+      <c r="M3" s="1">
         <f t="shared" ref="M3:M5" si="3">COUNTIF($E$2:$E$16,L3)</f>
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A4">
+    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A4" s="1">
         <v>103</v>
       </c>
-      <c r="B4" t="s">
+      <c r="B4" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C4">
+      <c r="C4" s="1">
         <v>12</v>
       </c>
-      <c r="D4" t="s">
+      <c r="D4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E4" t="s">
+      <c r="E4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F4">
+      <c r="F4" s="1">
         <v>90</v>
       </c>
-      <c r="H4" t="str">
+      <c r="H4" s="1" t="str">
         <f t="shared" si="0"/>
         <v>English</v>
       </c>
-      <c r="I4">
+      <c r="I4" s="1">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="J4" t="s">
+      <c r="J4" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="K4">
+      <c r="K4" s="1">
         <f t="shared" si="2"/>
         <v>4</v>
       </c>
-      <c r="L4" t="s">
+      <c r="L4" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="M4">
+      <c r="M4" s="1">
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A5">
+    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A5" s="1">
         <v>104</v>
       </c>
-      <c r="B5" t="s">
+      <c r="B5" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C5">
+      <c r="C5" s="1">
         <v>6</v>
       </c>
-      <c r="D5" t="s">
+      <c r="D5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E5" t="s">
+      <c r="E5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F5">
+      <c r="F5" s="1">
         <v>70</v>
       </c>
-      <c r="H5" t="str">
+      <c r="H5" s="1" t="str">
         <f t="shared" si="0"/>
         <v>History</v>
       </c>
-      <c r="I5">
+      <c r="I5" s="1">
         <f t="shared" si="1"/>
         <v>3</v>
       </c>
-      <c r="J5" t="s">
+      <c r="J5" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="K5">
+      <c r="K5" s="1">
         <f t="shared" si="2"/>
         <v>3</v>
       </c>
-      <c r="L5" t="s">
+      <c r="L5" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="M5">
+      <c r="M5" s="1">
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A6">
+    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A6" s="1">
         <v>105</v>
       </c>
-      <c r="B6" t="s">
+      <c r="B6" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C6">
+      <c r="C6" s="1">
         <v>15</v>
       </c>
-      <c r="D6" t="s">
+      <c r="D6" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E6" t="s">
+      <c r="E6" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F6">
+      <c r="F6" s="1">
         <v>92</v>
       </c>
-    </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A7">
+      <c r="M6" s="1">
+        <f>MATCH(MAX($M$2:$M$5),$M$2:$M$5,0)</f>
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A7" s="1">
         <v>106</v>
       </c>
-      <c r="B7" t="s">
+      <c r="B7" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C7">
+      <c r="C7" s="1">
         <v>7</v>
       </c>
-      <c r="D7" t="s">
+      <c r="D7" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E7" t="s">
+      <c r="E7" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F7">
+      <c r="F7" s="1">
         <v>80</v>
       </c>
-      <c r="I7" t="str">
+      <c r="I7" s="1" t="str">
         <f>INDEX($H$2:$H$5, MATCH(MAX($I2:$I$5),$I$2:$I$5,0),1)</f>
         <v>Science</v>
       </c>
-    </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A8">
+      <c r="J7" s="1">
+        <f>MAX($K$2:$K$5)</f>
+        <v>5</v>
+      </c>
+      <c r="M7" s="1">
+        <f>MAX($M$2:$M$5)</f>
+        <v>6</v>
+      </c>
+    </row>
+    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A8" s="1">
         <v>107</v>
       </c>
-      <c r="B8" t="s">
+      <c r="B8" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C8">
+      <c r="C8" s="1">
         <v>9</v>
       </c>
-      <c r="D8" t="s">
+      <c r="D8" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E8" t="s">
+      <c r="E8" s="1" t="s">
         <v>17</v>
       </c>
-      <c r="F8">
+      <c r="F8" s="1">
         <v>75</v>
       </c>
-    </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A9">
+      <c r="M8" s="1" t="str">
+        <f>INDEX($L$2:$L$5,MATCH(MAX($M$2:$M$5),$M$2:$M$5,0))</f>
+        <v>Laptop</v>
+      </c>
+    </row>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A9" s="1">
         <v>108</v>
       </c>
-      <c r="B9" t="s">
+      <c r="B9" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C9">
+      <c r="C9" s="1">
         <v>5</v>
       </c>
-      <c r="D9" t="s">
+      <c r="D9" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E9" t="s">
+      <c r="E9" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F9">
+      <c r="F9" s="1">
         <v>65</v>
       </c>
-    </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A10">
+      <c r="I9" s="1">
+        <f>AVERAGE(C2:C16)</f>
+        <v>10.066666666666666</v>
+      </c>
+      <c r="J9" s="1" t="str">
+        <f>INDEX($J$2:$J$5,MATCH(MAX($K$2:$K$5),$K$2:$K$5,0),1)</f>
+        <v>Visual</v>
+      </c>
+    </row>
+    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A10" s="1">
         <v>109</v>
       </c>
-      <c r="B10" t="s">
+      <c r="B10" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C10">
+      <c r="C10" s="1">
         <v>14</v>
       </c>
-      <c r="D10" t="s">
+      <c r="D10" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E10" t="s">
+      <c r="E10" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F10">
+      <c r="F10" s="1">
         <v>88</v>
       </c>
-    </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A11">
+      <c r="I10" s="1">
+        <f>ROUND(AVERAGE(C2:C16),2)</f>
+        <v>10.07</v>
+      </c>
+      <c r="J10" s="1" t="str">
+        <f>INDEX($J$2:$J$5,MATCH(MAX($K$2:$K$5),$K$2:$K$5,0))</f>
+        <v>Visual</v>
+      </c>
+    </row>
+    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A11" s="1">
         <v>110</v>
       </c>
-      <c r="B11" t="s">
+      <c r="B11" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C11">
+      <c r="C11" s="1">
         <v>11</v>
       </c>
-      <c r="D11" t="s">
+      <c r="D11" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E11" t="s">
+      <c r="E11" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F11">
+      <c r="F11" s="1">
         <v>82</v>
       </c>
-    </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A12">
+      <c r="K11" s="1">
+        <f>CORREL(C2:C16,F2:F16)</f>
+        <v>0.84621555000184756</v>
+      </c>
+    </row>
+    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A12" s="1">
         <v>111</v>
       </c>
-      <c r="B12" t="s">
+      <c r="B12" s="1" t="s">
         <v>12</v>
       </c>
-      <c r="C12">
+      <c r="C12" s="1">
         <v>13</v>
       </c>
-      <c r="D12" t="s">
+      <c r="D12" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E12" t="s">
+      <c r="E12" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F12">
+      <c r="F12" s="1">
         <v>91</v>
       </c>
-    </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A13">
+      <c r="K12" s="1">
+        <f>ROUND(AVERAGE(C2:C16,F2:F16),2)</f>
+        <v>45.57</v>
+      </c>
+    </row>
+    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A13" s="1">
         <v>112</v>
       </c>
-      <c r="B13" t="s">
+      <c r="B13" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C13">
+      <c r="C13" s="1">
         <v>9</v>
       </c>
-      <c r="D13" t="s">
+      <c r="D13" s="1" t="s">
         <v>10</v>
       </c>
-      <c r="E13" t="s">
+      <c r="E13" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F13">
+      <c r="F13" s="1">
         <v>77</v>
       </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A14">
+    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A14" s="1">
         <v>113</v>
       </c>
-      <c r="B14" t="s">
+      <c r="B14" s="1" t="s">
         <v>6</v>
       </c>
-      <c r="C14">
+      <c r="C14" s="1">
         <v>16</v>
       </c>
-      <c r="D14" t="s">
+      <c r="D14" s="1" t="s">
         <v>16</v>
       </c>
-      <c r="E14" t="s">
+      <c r="E14" s="1" t="s">
         <v>11</v>
       </c>
-      <c r="F14">
+      <c r="F14" s="1">
         <v>84</v>
       </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A15">
+    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A15" s="1">
         <v>114</v>
       </c>
-      <c r="B15" t="s">
+      <c r="B15" s="1" t="s">
         <v>15</v>
       </c>
-      <c r="C15">
+      <c r="C15" s="1">
         <v>6</v>
       </c>
-      <c r="D15" t="s">
+      <c r="D15" s="1" t="s">
         <v>13</v>
       </c>
-      <c r="E15" t="s">
+      <c r="E15" s="1" t="s">
         <v>8</v>
       </c>
-      <c r="F15">
+      <c r="F15" s="1">
         <v>73</v>
       </c>
-    </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.35">
-      <c r="A16">
+      <c r="H15" s="1" t="str">
+        <f>_xlfn.XLOOKUP(MAX($I$2:$I$5), $I$2:$I$5,$J$2:$J$5,"",0.1)</f>
+        <v>Auditory</v>
+      </c>
+    </row>
+    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
+      <c r="A16" s="1">
         <v>115</v>
       </c>
-      <c r="B16" t="s">
+      <c r="B16" s="1" t="s">
         <v>9</v>
       </c>
-      <c r="C16">
+      <c r="C16" s="1">
         <v>10</v>
       </c>
-      <c r="D16" t="s">
+      <c r="D16" s="1" t="s">
         <v>7</v>
       </c>
-      <c r="E16" t="s">
+      <c r="E16" s="1" t="s">
         <v>14</v>
       </c>
-      <c r="F16">
+      <c r="F16" s="1">
         <v>86</v>
       </c>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:E7"/>
   <sheetFormatPr defaultRowHeight="14.5" x14ac:dyDescent="0.35"/>
   <sheetData>

--- a/excel-projects/class_survey_results_v2.xlsx
+++ b/excel-projects/class_survey_results_v2.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\data-analytics-repo\excel-projects\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1539C587-180A-4943-B5DD-F719713DB0AF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DC079671-7E65-4473-9B66-EA81CCB0E1F6}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10300" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -34,7 +34,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="30">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="75" uniqueCount="32">
   <si>
     <t>Student ID</t>
   </si>
@@ -124,6 +124,12 @@
   </si>
   <si>
     <t>musa</t>
+  </si>
+  <si>
+    <t>study hour</t>
+  </si>
+  <si>
+    <t>Test score</t>
   </si>
 </sst>
 </file>
@@ -673,6 +679,1098 @@
     </ext>
   </extLst>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<c:chartSpace xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:c16r2="http://schemas.microsoft.com/office/drawing/2015/06/chart">
+  <c:date1904 val="0"/>
+  <c:lang val="en-US"/>
+  <c:roundedCorners val="0"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice xmlns:c14="http://schemas.microsoft.com/office/drawing/2007/8/2/chart" Requires="c14">
+      <c14:style val="102"/>
+    </mc:Choice>
+    <mc:Fallback>
+      <c:style val="2"/>
+    </mc:Fallback>
+  </mc:AlternateContent>
+  <c:chart>
+    <c:title>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="1400" b="0" i="0" u="none" strike="noStrike" kern="1200" spc="0" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:title>
+    <c:autoTitleDeleted val="0"/>
+    <c:plotArea>
+      <c:layout/>
+      <c:barChart>
+        <c:barDir val="col"/>
+        <c:grouping val="clustered"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="0"/>
+          <c:order val="0"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>class_survey_results_v2!$N$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>study hour</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:solidFill>
+              <a:schemeClr val="accent1"/>
+            </a:solidFill>
+            <a:ln>
+              <a:noFill/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:invertIfNegative val="0"/>
+          <c:val>
+            <c:numRef>
+              <c:f>class_survey_results_v2!$N$2:$N$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>5</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>6</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>9</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>8</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>7</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>11</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>16</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>10</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>14</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>12</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>13</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>15</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000000-EC5E-421E-8CF4-D2AC6D993616}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:gapWidth val="150"/>
+        <c:axId val="367225232"/>
+        <c:axId val="367225712"/>
+      </c:barChart>
+      <c:lineChart>
+        <c:grouping val="standard"/>
+        <c:varyColors val="0"/>
+        <c:ser>
+          <c:idx val="1"/>
+          <c:order val="1"/>
+          <c:tx>
+            <c:strRef>
+              <c:f>class_survey_results_v2!$O$1</c:f>
+              <c:strCache>
+                <c:ptCount val="1"/>
+                <c:pt idx="0">
+                  <c:v>Test score</c:v>
+                </c:pt>
+              </c:strCache>
+            </c:strRef>
+          </c:tx>
+          <c:spPr>
+            <a:ln w="28575" cap="rnd">
+              <a:solidFill>
+                <a:schemeClr val="accent2"/>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+          <c:marker>
+            <c:symbol val="none"/>
+          </c:marker>
+          <c:val>
+            <c:numRef>
+              <c:f>class_survey_results_v2!$O$2:$O$16</c:f>
+              <c:numCache>
+                <c:formatCode>General</c:formatCode>
+                <c:ptCount val="15"/>
+                <c:pt idx="0">
+                  <c:v>65</c:v>
+                </c:pt>
+                <c:pt idx="1">
+                  <c:v>70</c:v>
+                </c:pt>
+                <c:pt idx="2">
+                  <c:v>73</c:v>
+                </c:pt>
+                <c:pt idx="3">
+                  <c:v>75</c:v>
+                </c:pt>
+                <c:pt idx="4">
+                  <c:v>77</c:v>
+                </c:pt>
+                <c:pt idx="5">
+                  <c:v>78</c:v>
+                </c:pt>
+                <c:pt idx="6">
+                  <c:v>80</c:v>
+                </c:pt>
+                <c:pt idx="7">
+                  <c:v>82</c:v>
+                </c:pt>
+                <c:pt idx="8">
+                  <c:v>84</c:v>
+                </c:pt>
+                <c:pt idx="9">
+                  <c:v>85</c:v>
+                </c:pt>
+                <c:pt idx="10">
+                  <c:v>86</c:v>
+                </c:pt>
+                <c:pt idx="11">
+                  <c:v>88</c:v>
+                </c:pt>
+                <c:pt idx="12">
+                  <c:v>90</c:v>
+                </c:pt>
+                <c:pt idx="13">
+                  <c:v>91</c:v>
+                </c:pt>
+                <c:pt idx="14">
+                  <c:v>92</c:v>
+                </c:pt>
+              </c:numCache>
+            </c:numRef>
+          </c:val>
+          <c:smooth val="0"/>
+          <c:extLst>
+            <c:ext xmlns:c16="http://schemas.microsoft.com/office/drawing/2014/chart" uri="{C3380CC4-5D6E-409C-BE32-E72D297353CC}">
+              <c16:uniqueId val="{00000001-EC5E-421E-8CF4-D2AC6D993616}"/>
+            </c:ext>
+          </c:extLst>
+        </c:ser>
+        <c:dLbls>
+          <c:showLegendKey val="0"/>
+          <c:showVal val="0"/>
+          <c:showCatName val="0"/>
+          <c:showSerName val="0"/>
+          <c:showPercent val="0"/>
+          <c:showBubbleSize val="0"/>
+        </c:dLbls>
+        <c:marker val="1"/>
+        <c:smooth val="0"/>
+        <c:axId val="793672864"/>
+        <c:axId val="793677184"/>
+      </c:lineChart>
+      <c:catAx>
+        <c:axId val="367225232"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+            <a:solidFill>
+              <a:schemeClr val="tx1">
+                <a:lumMod val="15000"/>
+                <a:lumOff val="85000"/>
+              </a:schemeClr>
+            </a:solidFill>
+            <a:round/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="367225712"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:valAx>
+        <c:axId val="367225712"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="l"/>
+        <c:majorGridlines>
+          <c:spPr>
+            <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="15000"/>
+                  <a:lumOff val="85000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:round/>
+            </a:ln>
+            <a:effectLst/>
+          </c:spPr>
+        </c:majorGridlines>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="none"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="367225232"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:valAx>
+        <c:axId val="793677184"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="0"/>
+        <c:axPos val="r"/>
+        <c:numFmt formatCode="General" sourceLinked="1"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:spPr>
+          <a:noFill/>
+          <a:ln>
+            <a:noFill/>
+          </a:ln>
+          <a:effectLst/>
+        </c:spPr>
+        <c:txPr>
+          <a:bodyPr rot="-60000000" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+          <a:lstStyle/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+                <a:solidFill>
+                  <a:schemeClr val="tx1">
+                    <a:lumMod val="65000"/>
+                    <a:lumOff val="35000"/>
+                  </a:schemeClr>
+                </a:solidFill>
+                <a:latin typeface="+mn-lt"/>
+                <a:ea typeface="+mn-ea"/>
+                <a:cs typeface="+mn-cs"/>
+              </a:defRPr>
+            </a:pPr>
+            <a:endParaRPr lang="en-US"/>
+          </a:p>
+        </c:txPr>
+        <c:crossAx val="793672864"/>
+        <c:crosses val="max"/>
+        <c:crossBetween val="between"/>
+      </c:valAx>
+      <c:catAx>
+        <c:axId val="793672864"/>
+        <c:scaling>
+          <c:orientation val="minMax"/>
+        </c:scaling>
+        <c:delete val="1"/>
+        <c:axPos val="b"/>
+        <c:majorTickMark val="out"/>
+        <c:minorTickMark val="none"/>
+        <c:tickLblPos val="nextTo"/>
+        <c:crossAx val="793677184"/>
+        <c:auto val="1"/>
+        <c:lblAlgn val="ctr"/>
+        <c:lblOffset val="100"/>
+        <c:noMultiLvlLbl val="0"/>
+      </c:catAx>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+    </c:plotArea>
+    <c:legend>
+      <c:legendPos val="b"/>
+      <c:overlay val="0"/>
+      <c:spPr>
+        <a:noFill/>
+        <a:ln>
+          <a:noFill/>
+        </a:ln>
+        <a:effectLst/>
+      </c:spPr>
+      <c:txPr>
+        <a:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="ellipsis" vert="horz" wrap="square" anchor="ctr" anchorCtr="1"/>
+        <a:lstStyle/>
+        <a:p>
+          <a:pPr>
+            <a:defRPr sz="900" b="0" i="0" u="none" strike="noStrike" kern="1200" baseline="0">
+              <a:solidFill>
+                <a:schemeClr val="tx1">
+                  <a:lumMod val="65000"/>
+                  <a:lumOff val="35000"/>
+                </a:schemeClr>
+              </a:solidFill>
+              <a:latin typeface="+mn-lt"/>
+              <a:ea typeface="+mn-ea"/>
+              <a:cs typeface="+mn-cs"/>
+            </a:defRPr>
+          </a:pPr>
+          <a:endParaRPr lang="en-US"/>
+        </a:p>
+      </c:txPr>
+    </c:legend>
+    <c:plotVisOnly val="1"/>
+    <c:dispBlanksAs val="gap"/>
+    <c:extLst>
+      <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
+        <c16r3:dataDisplayOptions16>
+          <c16r3:dispNaAsBlank val="1"/>
+        </c16r3:dataDisplayOptions16>
+      </c:ext>
+    </c:extLst>
+    <c:showDLblsOverMax val="0"/>
+  </c:chart>
+  <c:spPr>
+    <a:solidFill>
+      <a:schemeClr val="bg1"/>
+    </a:solidFill>
+    <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+      <a:solidFill>
+        <a:schemeClr val="tx1">
+          <a:lumMod val="15000"/>
+          <a:lumOff val="85000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:round/>
+    </a:ln>
+    <a:effectLst/>
+  </c:spPr>
+  <c:txPr>
+    <a:bodyPr/>
+    <a:lstStyle/>
+    <a:p>
+      <a:pPr>
+        <a:defRPr/>
+      </a:pPr>
+      <a:endParaRPr lang="en-US"/>
+    </a:p>
+  </c:txPr>
+  <c:printSettings>
+    <c:headerFooter/>
+    <c:pageMargins b="0.75" l="0.7" r="0.7" t="0.75" header="0.3" footer="0.3"/>
+    <c:pageSetup/>
+  </c:printSettings>
+</c:chartSpace>
+</file>
+
+<file path=xl/charts/colors1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:colorStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" meth="cycle" id="10">
+  <a:schemeClr val="accent1"/>
+  <a:schemeClr val="accent2"/>
+  <a:schemeClr val="accent3"/>
+  <a:schemeClr val="accent4"/>
+  <a:schemeClr val="accent5"/>
+  <a:schemeClr val="accent6"/>
+  <cs:variation/>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+    <a:lumOff val="20000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="80000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="60000"/>
+    <a:lumOff val="40000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+    <a:lumOff val="30000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="70000"/>
+  </cs:variation>
+  <cs:variation>
+    <a:lumMod val="50000"/>
+    <a:lumOff val="50000"/>
+  </cs:variation>
+</cs:colorStyle>
+</file>
+
+<file path=xl/charts/style1.xml><?xml version="1.0" encoding="utf-8"?>
+<cs:chartStyle xmlns:cs="http://schemas.microsoft.com/office/drawing/2012/chartStyle" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" id="322">
+  <cs:axisTitle>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:axisTitle>
+  <cs:categoryAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:categoryAxis>
+  <cs:chartArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="bg1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="1000" kern="1200"/>
+  </cs:chartArea>
+  <cs:dataLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="75000"/>
+        <a:lumOff val="25000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataLabel>
+  <cs:dataLabelCallout>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="dk1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln>
+        <a:solidFill>
+          <a:schemeClr val="dk1">
+            <a:lumMod val="25000"/>
+            <a:lumOff val="75000"/>
+          </a:schemeClr>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+    <cs:bodyPr rot="0" spcFirstLastPara="1" vertOverflow="clip" horzOverflow="clip" vert="horz" wrap="square" lIns="36576" tIns="18288" rIns="36576" bIns="18288" anchor="ctr" anchorCtr="1">
+      <a:spAutoFit/>
+    </cs:bodyPr>
+  </cs:dataLabelCallout>
+  <cs:dataPoint>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint>
+  <cs:dataPoint3D>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:dataPoint3D>
+  <cs:dataPointLine>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="28575" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointLine>
+  <cs:dataPointMarker>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1">
+      <cs:styleClr val="auto"/>
+    </cs:fillRef>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointMarker>
+  <cs:dataPointMarkerLayout symbol="circle" size="5"/>
+  <cs:dataPointWireframe>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="1"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dataPointWireframe>
+  <cs:dataTable>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:dataTable>
+  <cs:downBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="dk1">
+          <a:lumMod val="75000"/>
+          <a:lumOff val="25000"/>
+        </a:schemeClr>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:downBar>
+  <cs:dropLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:dropLine>
+  <cs:errorBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:errorBar>
+  <cs:floor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:floor>
+  <cs:gridlineMajor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMajor>
+  <cs:gridlineMinor>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="5000"/>
+            <a:lumOff val="95000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:gridlineMinor>
+  <cs:hiLoLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="75000"/>
+            <a:lumOff val="25000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:hiLoLine>
+  <cs:leaderLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:leaderLine>
+  <cs:legend>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:legend>
+  <cs:plotArea mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea>
+  <cs:plotArea3D mods="allowNoFillOverride allowNoLineOverride">
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+  </cs:plotArea3D>
+  <cs:seriesAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="15000"/>
+            <a:lumOff val="85000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:seriesAxis>
+  <cs:seriesLine>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="35000"/>
+            <a:lumOff val="65000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:seriesLine>
+  <cs:title>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="1400" b="0" kern="1200" spc="0" baseline="0"/>
+  </cs:title>
+  <cs:trendline>
+    <cs:lnRef idx="0">
+      <cs:styleClr val="auto"/>
+    </cs:lnRef>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:ln w="19050" cap="rnd">
+        <a:solidFill>
+          <a:schemeClr val="phClr"/>
+        </a:solidFill>
+        <a:prstDash val="sysDot"/>
+      </a:ln>
+    </cs:spPr>
+  </cs:trendline>
+  <cs:trendlineLabel>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:trendlineLabel>
+  <cs:upBar>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:solidFill>
+        <a:schemeClr val="lt1"/>
+      </a:solidFill>
+      <a:ln w="9525" cap="flat" cmpd="sng" algn="ctr">
+        <a:solidFill>
+          <a:schemeClr val="tx1">
+            <a:lumMod val="65000"/>
+            <a:lumOff val="35000"/>
+          </a:schemeClr>
+        </a:solidFill>
+        <a:round/>
+      </a:ln>
+    </cs:spPr>
+  </cs:upBar>
+  <cs:valueAxis>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1">
+        <a:lumMod val="65000"/>
+        <a:lumOff val="35000"/>
+      </a:schemeClr>
+    </cs:fontRef>
+    <cs:defRPr sz="900" kern="1200"/>
+  </cs:valueAxis>
+  <cs:wall>
+    <cs:lnRef idx="0"/>
+    <cs:fillRef idx="0"/>
+    <cs:effectRef idx="0"/>
+    <cs:fontRef idx="minor">
+      <a:schemeClr val="tx1"/>
+    </cs:fontRef>
+    <cs:spPr>
+      <a:noFill/>
+      <a:ln>
+        <a:noFill/>
+      </a:ln>
+    </cs:spPr>
+  </cs:wall>
+</cs:chartStyle>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<xdr:wsDr xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main">
+  <xdr:twoCellAnchor>
+    <xdr:from>
+      <xdr:col>15</xdr:col>
+      <xdr:colOff>194469</xdr:colOff>
+      <xdr:row>1</xdr:row>
+      <xdr:rowOff>148432</xdr:rowOff>
+    </xdr:from>
+    <xdr:to>
+      <xdr:col>22</xdr:col>
+      <xdr:colOff>488157</xdr:colOff>
+      <xdr:row>13</xdr:row>
+      <xdr:rowOff>34132</xdr:rowOff>
+    </xdr:to>
+    <xdr:graphicFrame macro="">
+      <xdr:nvGraphicFramePr>
+        <xdr:cNvPr id="2" name="Chart 1">
+          <a:extLst>
+            <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{400BE534-82BD-3EDD-5E67-7FA57BF86C99}"/>
+            </a:ext>
+          </a:extLst>
+        </xdr:cNvPr>
+        <xdr:cNvGraphicFramePr/>
+      </xdr:nvGraphicFramePr>
+      <xdr:xfrm>
+        <a:off x="0" y="0"/>
+        <a:ext cx="0" cy="0"/>
+      </xdr:xfrm>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </xdr:graphicFrame>
+    <xdr:clientData/>
+  </xdr:twoCellAnchor>
+</xdr:wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -958,7 +2056,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:M16"/>
+  <dimension ref="A1:O16"/>
   <sheetFormatPr defaultRowHeight="18.5" x14ac:dyDescent="0.45"/>
   <cols>
     <col min="1" max="1" width="15.90625" style="1" customWidth="1"/>
@@ -972,10 +2070,13 @@
     <col min="10" max="10" width="16.1796875" style="1" customWidth="1"/>
     <col min="11" max="11" width="9.6328125" style="1" customWidth="1"/>
     <col min="12" max="12" width="14" style="1" customWidth="1"/>
-    <col min="13" max="16384" width="8.7265625" style="1"/>
+    <col min="13" max="13" width="11.453125" style="1" customWidth="1"/>
+    <col min="14" max="14" width="15.1796875" style="1" customWidth="1"/>
+    <col min="15" max="15" width="11.26953125" style="1" customWidth="1"/>
+    <col min="16" max="16384" width="8.7265625" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A1" s="1" t="s">
         <v>0</v>
       </c>
@@ -1012,8 +2113,14 @@
       <c r="M1" s="1" t="s">
         <v>19</v>
       </c>
+      <c r="N1" s="1" t="s">
+        <v>30</v>
+      </c>
+      <c r="O1" s="1" t="s">
+        <v>31</v>
+      </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="2" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A2" s="1">
         <v>101</v>
       </c>
@@ -1054,8 +2161,14 @@
         <f>COUNTIF($E$2:$E$16,L2)</f>
         <v>6</v>
       </c>
+      <c r="N2" s="1">
+        <v>5</v>
+      </c>
+      <c r="O2" s="1">
+        <v>65</v>
+      </c>
     </row>
-    <row r="3" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="3" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A3" s="1">
         <v>102</v>
       </c>
@@ -1096,8 +2209,14 @@
         <f t="shared" ref="M3:M5" si="3">COUNTIF($E$2:$E$16,L3)</f>
         <v>4</v>
       </c>
+      <c r="N3" s="1">
+        <v>6</v>
+      </c>
+      <c r="O3" s="1">
+        <v>70</v>
+      </c>
     </row>
-    <row r="4" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="4" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A4" s="1">
         <v>103</v>
       </c>
@@ -1138,8 +2257,14 @@
         <f t="shared" si="3"/>
         <v>3</v>
       </c>
+      <c r="N4" s="1">
+        <v>6</v>
+      </c>
+      <c r="O4" s="1">
+        <v>73</v>
+      </c>
     </row>
-    <row r="5" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="5" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A5" s="1">
         <v>104</v>
       </c>
@@ -1180,8 +2305,14 @@
         <f t="shared" si="3"/>
         <v>2</v>
       </c>
+      <c r="N5" s="1">
+        <v>9</v>
+      </c>
+      <c r="O5" s="1">
+        <v>75</v>
+      </c>
     </row>
-    <row r="6" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="6" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A6" s="1">
         <v>105</v>
       </c>
@@ -1204,8 +2335,14 @@
         <f>MATCH(MAX($M$2:$M$5),$M$2:$M$5,0)</f>
         <v>1</v>
       </c>
+      <c r="N6" s="1">
+        <v>9</v>
+      </c>
+      <c r="O6" s="1">
+        <v>77</v>
+      </c>
     </row>
-    <row r="7" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="7" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A7" s="1">
         <v>106</v>
       </c>
@@ -1236,8 +2373,14 @@
         <f>MAX($M$2:$M$5)</f>
         <v>6</v>
       </c>
+      <c r="N7" s="1">
+        <v>8</v>
+      </c>
+      <c r="O7" s="1">
+        <v>78</v>
+      </c>
     </row>
-    <row r="8" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="8" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A8" s="1">
         <v>107</v>
       </c>
@@ -1260,8 +2403,14 @@
         <f>INDEX($L$2:$L$5,MATCH(MAX($M$2:$M$5),$M$2:$M$5,0))</f>
         <v>Laptop</v>
       </c>
+      <c r="N8" s="1">
+        <v>7</v>
+      </c>
+      <c r="O8" s="1">
+        <v>80</v>
+      </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="9" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A9" s="1">
         <v>108</v>
       </c>
@@ -1288,8 +2437,14 @@
         <f>INDEX($J$2:$J$5,MATCH(MAX($K$2:$K$5),$K$2:$K$5,0),1)</f>
         <v>Visual</v>
       </c>
+      <c r="N9" s="1">
+        <v>11</v>
+      </c>
+      <c r="O9" s="1">
+        <v>82</v>
+      </c>
     </row>
-    <row r="10" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="10" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A10" s="1">
         <v>109</v>
       </c>
@@ -1316,8 +2471,14 @@
         <f>INDEX($J$2:$J$5,MATCH(MAX($K$2:$K$5),$K$2:$K$5,0))</f>
         <v>Visual</v>
       </c>
+      <c r="N10" s="1">
+        <v>16</v>
+      </c>
+      <c r="O10" s="1">
+        <v>84</v>
+      </c>
     </row>
-    <row r="11" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="11" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A11" s="1">
         <v>110</v>
       </c>
@@ -1337,11 +2498,17 @@
         <v>82</v>
       </c>
       <c r="K11" s="1">
-        <f>CORREL(C2:C16,F2:F16)</f>
+        <f>CORREL($C$2:$C$16,$F$2:$F$16)</f>
         <v>0.84621555000184756</v>
       </c>
+      <c r="N11" s="1">
+        <v>10</v>
+      </c>
+      <c r="O11" s="1">
+        <v>85</v>
+      </c>
     </row>
-    <row r="12" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="12" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A12" s="1">
         <v>111</v>
       </c>
@@ -1361,11 +2528,17 @@
         <v>91</v>
       </c>
       <c r="K12" s="1">
-        <f>ROUND(AVERAGE(C2:C16,F2:F16),2)</f>
-        <v>45.57</v>
+        <f>ROUND(AVERAGE(C2:C16,F2:F16),1)</f>
+        <v>45.6</v>
+      </c>
+      <c r="N12" s="1">
+        <v>10</v>
+      </c>
+      <c r="O12" s="1">
+        <v>86</v>
       </c>
     </row>
-    <row r="13" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="13" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A13" s="1">
         <v>112</v>
       </c>
@@ -1384,8 +2557,14 @@
       <c r="F13" s="1">
         <v>77</v>
       </c>
+      <c r="N13" s="1">
+        <v>14</v>
+      </c>
+      <c r="O13" s="1">
+        <v>88</v>
+      </c>
     </row>
-    <row r="14" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="14" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A14" s="1">
         <v>113</v>
       </c>
@@ -1404,8 +2583,14 @@
       <c r="F14" s="1">
         <v>84</v>
       </c>
+      <c r="N14" s="1">
+        <v>12</v>
+      </c>
+      <c r="O14" s="1">
+        <v>90</v>
+      </c>
     </row>
-    <row r="15" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="15" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A15" s="1">
         <v>114</v>
       </c>
@@ -1428,8 +2613,14 @@
         <f>_xlfn.XLOOKUP(MAX($I$2:$I$5), $I$2:$I$5,$J$2:$J$5,"",0.1)</f>
         <v>Auditory</v>
       </c>
+      <c r="N15" s="1">
+        <v>13</v>
+      </c>
+      <c r="O15" s="1">
+        <v>91</v>
+      </c>
     </row>
-    <row r="16" spans="1:13" x14ac:dyDescent="0.45">
+    <row r="16" spans="1:15" x14ac:dyDescent="0.45">
       <c r="A16" s="1">
         <v>115</v>
       </c>
@@ -1448,10 +2639,20 @@
       <c r="F16" s="1">
         <v>86</v>
       </c>
+      <c r="N16" s="1">
+        <v>15</v>
+      </c>
+      <c r="O16" s="1">
+        <v>92</v>
+      </c>
     </row>
   </sheetData>
+  <sortState xmlns:xlrd2="http://schemas.microsoft.com/office/spreadsheetml/2017/richdata2" ref="N2:O16">
+    <sortCondition ref="O2:O16"/>
+  </sortState>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup orientation="portrait" horizontalDpi="0" verticalDpi="0" r:id="rId1"/>
+  <drawing r:id="rId2"/>
 </worksheet>
 </file>
 
